--- a/public/reports/BHARTIARTL_NS_Financial_Model.xlsx
+++ b/public/reports/BHARTIARTL_NS_Financial_Model.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="692">
   <si>
     <t>Bharti Airtel Limited (BHARTIARTL.NS)</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Fair value per share (INR)</t>
   </si>
   <si>
-    <t>Upside / (downside)</t>
+    <t>Model valuation spread vs price (an unaudited model output, not a rating; not independently audited)</t>
   </si>
   <si>
     <t>Primary method</t>
@@ -75,7 +75,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Telecommunications &amp; Digital Network Infrastructure valued via FCFF_DCF_3STAGE. 59/59 accounting invariants passed; reasonableness verdict REQUIRES_ANALYST_JUSTIFICATION.</t>
+    <t>Telecommunications &amp; Digital Network Infrastructure valued via FCFF_DCF_3STAGE. 59/59 accounting invariants passed; reasonableness assessment REQUIRES_ANALYST_JUSTIFICATION.</t>
   </si>
   <si>
     <t>KEY FINANCIALS (₹ Crores)</t>
@@ -204,19 +204,19 @@
     <t>Snapshot ID</t>
   </si>
   <si>
-    <t>snap_BHARTIARTL_NS_24392f289409</t>
+    <t>snap_BHARTIARTL_NS_9743f134043d</t>
   </si>
   <si>
     <t>Snapshot SHA-256</t>
   </si>
   <si>
-    <t>24392f289409666d0e762d32625c202a7f04b9ccbc4e042222fa8ae2b255fd9e</t>
+    <t>9743f134043d75387245643b89a5b1ce52f88ae2bc83adb18db216095b42524c</t>
   </si>
   <si>
     <t>Built at</t>
   </si>
   <si>
-    <t>2026-11-01T14:58:12.989Z</t>
+    <t>2026-11-01T15:05:01.347Z</t>
   </si>
   <si>
     <t>Analysis status</t>
@@ -288,7 +288,7 @@
     <t>2359.67</t>
   </si>
   <si>
-    <t>Upside / (downside) %</t>
+    <t>Model valuation spread vs price (an unaudited model output, not a rating; not independently audited) %</t>
   </si>
   <si>
     <t>19.56</t>
@@ -963,7 +963,7 @@
     <t>Implied terminal ROIC (%)</t>
   </si>
   <si>
-    <t>Verdict</t>
+    <t>Assessment</t>
   </si>
   <si>
     <t>balanced realistic expectations</t>
@@ -1239,7 +1239,7 @@
     <t>Forensic audit complete: Overall Health: UNAVAILABLE | Altman Z: N/A (N/A) | Piotroski F: N/A/9 | Beneish M: N/A (N/A).</t>
   </si>
   <si>
-    <t>ACCOUNTING QUALITY (verdict CAUTION)</t>
+    <t>ACCOUNTING QUALITY (assessment CAUTION)</t>
   </si>
   <si>
     <t>Check</t>
@@ -1800,40 +1800,16 @@
     <t>Assumptions hash (12)</t>
   </si>
   <si>
-    <t>snap_BHARTIARTL_NS_24392f289409  &lt;- THIS WORKBOOK</t>
+    <t>snap_BHARTIARTL_NS_9743f134043d  &lt;- THIS WORKBOOK</t>
   </si>
   <si>
     <t>74234e98afe7</t>
   </si>
   <si>
-    <t>snap_BHARTIARTL_NS_7195e2e64806</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:58:12.919Z</t>
-  </si>
-  <si>
-    <t>snap_BHARTIARTL_NS_99ed6aabf652</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:56:15.406Z</t>
-  </si>
-  <si>
-    <t>snap_BHARTIARTL_NS_1cb45ecbf0ba</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:56:15.338Z</t>
-  </si>
-  <si>
-    <t>snap_BHARTIARTL_NS_8488fd8785e3</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:53:10.113Z</t>
-  </si>
-  <si>
-    <t>snap_BHARTIARTL_NS_6360ae76accb</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:53:10.033Z</t>
+    <t>snap_BHARTIARTL_NS_48eaf485b870</t>
+  </si>
+  <si>
+    <t>2026-11-01T15:05:01.276Z</t>
   </si>
   <si>
     <t>OVERRIDES APPLIED TO THIS WORKBOOK</t>
@@ -1938,7 +1914,7 @@
     <t>Difference</t>
   </si>
   <si>
-    <t>No DCF stance without a DCF</t>
+    <t>No DCF reading without a DCF</t>
   </si>
   <si>
     <t>VALUATION</t>
@@ -1947,7 +1923,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>DCF ran; stance derived from it only</t>
+    <t>DCF ran; reading derived from it only</t>
   </si>
   <si>
     <t>No bonus / split is classified as economic dilution</t>
@@ -2028,7 +2004,7 @@
     <t>SAVED RECORD AND VERIFIER RECEIPTS</t>
   </si>
   <si>
-    <t>This snapshot's saved record (provenance, publication states, discrepancies, peer selection, limits and every verifier receipt) is kept by FMB beside the exported files: GET /api/export/snapshot/snap_BHARTIARTL_NS_24392f289409/record. Receipts are appended as verifiers run (workbook formula re-derivation, independent Monte Carlo), so they are read from the record, not stored in this file.</t>
+    <t>This snapshot's saved record (provenance, publication states, discrepancies, peer selection, limits and every verifier receipt) is kept by FMB beside the exported files: GET /api/export/snapshot/snap_BHARTIARTL_NS_9743f134043d/record. Receipts are appended as verifiers run (workbook formula re-derivation, independent Monte Carlo), so they are read from the record, not stored in this file.</t>
   </si>
   <si>
     <t>Chart data (editable)</t>
@@ -9947,7 +9923,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
@@ -10068,186 +10044,62 @@
         <v>587</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>591</v>
       </c>
-      <c r="C8" s="15">
-        <v>1973.7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="15">
-        <v>2359.67</v>
-      </c>
-      <c r="G8" s="15">
-        <f>F8-2359.67</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="13">
-        <f>G8/2359.67</f>
-        <v>0</v>
-      </c>
-      <c r="I8" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>593</v>
       </c>
-      <c r="C9" s="15">
-        <v>1973.7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="15">
-        <v>2359.67</v>
-      </c>
-      <c r="G9" s="15">
-        <f>F9-2359.67</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="13">
-        <f>G9/2359.67</f>
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B13" t="s">
         <v>594</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C13" t="s">
         <v>595</v>
       </c>
-      <c r="C10" s="15">
-        <v>1973.7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="15">
-        <v>2359.67</v>
-      </c>
-      <c r="G10" s="15">
-        <f>F10-2359.67</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="13">
-        <f>G10/2359.67</f>
-        <v>0</v>
-      </c>
-      <c r="I10" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>593</v>
+      </c>
+      <c r="B14" t="s">
         <v>596</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C14" t="s">
         <v>597</v>
       </c>
-      <c r="C11" s="15">
-        <v>1973.7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F11" s="15">
-        <v>2359.67</v>
-      </c>
-      <c r="G11" s="15">
-        <f>F11-2359.67</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
-        <f>G11/2359.67</f>
-        <v>0</v>
-      </c>
-      <c r="I11" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>601</v>
-      </c>
-      <c r="B17" t="s">
-        <v>602</v>
-      </c>
-      <c r="C17" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>601</v>
-      </c>
-      <c r="B18" t="s">
-        <v>604</v>
-      </c>
-      <c r="C18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -10272,17 +10124,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -10294,7 +10146,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>479</v>
@@ -10306,27 +10158,27 @@
         <v>190</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>575</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="B6" t="s">
         <v>487</v>
@@ -10335,13 +10187,13 @@
         <v>139145</v>
       </c>
       <c r="D6" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="E6" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="F6" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="G6" t="s">
         <v>89</v>
@@ -10353,12 +10205,12 @@
         <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B7" t="s">
         <v>487</v>
@@ -10367,13 +10219,13 @@
         <v>12287</v>
       </c>
       <c r="D7" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="E7" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="F7" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="G7" t="s">
         <v>89</v>
@@ -10390,7 +10242,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="B8" t="s">
         <v>523</v>
@@ -10399,13 +10251,13 @@
         <v>149982</v>
       </c>
       <c r="D8" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="E8" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="F8" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="G8" t="s">
         <v>89</v>
@@ -10417,12 +10269,12 @@
         <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="B9" t="s">
         <v>523</v>
@@ -10431,13 +10283,13 @@
         <v>8558</v>
       </c>
       <c r="D9" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="E9" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="F9" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="G9" t="s">
         <v>89</v>
@@ -10454,7 +10306,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="B10" t="s">
         <v>538</v>
@@ -10463,13 +10315,13 @@
         <v>172985</v>
       </c>
       <c r="D10" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="E10" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="F10" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="G10" t="s">
         <v>89</v>
@@ -10481,12 +10333,12 @@
         <v>25</v>
       </c>
       <c r="J10" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="B11" t="s">
         <v>538</v>
@@ -10495,13 +10347,13 @@
         <v>37481</v>
       </c>
       <c r="D11" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="E11" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="F11" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="G11" t="s">
         <v>89</v>
@@ -10518,7 +10370,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="B12" t="s">
         <v>553</v>
@@ -10527,13 +10379,13 @@
         <v>210973</v>
       </c>
       <c r="D12" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="E12" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="F12" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="G12" t="s">
         <v>89</v>
@@ -10545,12 +10397,12 @@
         <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="B13" t="s">
         <v>553</v>
@@ -10559,13 +10411,13 @@
         <v>33823</v>
       </c>
       <c r="D13" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="E13" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="F13" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="G13" t="s">
         <v>89</v>
@@ -10582,7 +10434,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -10597,19 +10449,19 @@
         <v>400</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>404</v>
@@ -10617,13 +10469,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="B17" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="C17" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="D17" t="s">
         <v>25</v>
@@ -10635,18 +10487,18 @@
         <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="B18" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="C18" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="D18" t="s">
         <v>25</v>
@@ -10658,18 +10510,18 @@
         <v>25</v>
       </c>
       <c r="G18" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B19" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="C19" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="D19" t="s">
         <v>25</v>
@@ -10681,12 +10533,12 @@
         <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -10698,46 +10550,46 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="B24" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="C24" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="D24" t="s">
         <v>255</v>
       </c>
       <c r="E24" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -10749,10 +10601,10 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="B27" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -10781,10 +10633,10 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="B31" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -10797,7 +10649,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="B33" t="s">
         <v>345</v>
@@ -10805,7 +10657,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="B34" t="s">
         <v>243</v>
@@ -10816,7 +10668,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="B35" t="s">
         <v>246</v>
@@ -10827,7 +10679,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="B36" t="s">
         <v>248</v>
@@ -10838,7 +10690,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="B37" t="s">
         <v>250</v>
@@ -10849,15 +10701,15 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="B38" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -10869,7 +10721,7 @@
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -10889,17 +10741,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -10909,27 +10761,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="B6" s="35">
         <v>257.61085145830316</v>
@@ -10950,7 +10802,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="B7" s="35">
         <v>901.42487115811</v>
@@ -10971,7 +10823,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="B8" s="35">
         <v>1545.2388908579169</v>
@@ -10992,7 +10844,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="B9" s="35">
         <v>2189.0529105577234</v>
@@ -11013,7 +10865,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="B10" s="35">
         <v>2832.866930257531</v>
@@ -11034,7 +10886,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="B11" s="35">
         <v>3476.6809499573374</v>
@@ -11055,7 +10907,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="B12" s="35">
         <v>4120.494969657144</v>
@@ -11076,7 +10928,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="B13" s="35">
         <v>4764.308989356951</v>
@@ -11097,7 +10949,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="B14" s="35">
         <v>5408.123009056758</v>
@@ -11118,7 +10970,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="B15" s="35">
         <v>6051.937028756564</v>
@@ -11139,7 +10991,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -11152,21 +11004,21 @@
         <v>176</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B20" s="17">
         <v>1</v>
@@ -11178,12 +11030,12 @@
         <v>-0.014</v>
       </c>
       <c r="E20" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B21" s="17">
         <v>2</v>
@@ -11195,12 +11047,12 @@
         <v>0.009</v>
       </c>
       <c r="E21" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="B22" s="17">
         <v>3</v>
@@ -11212,12 +11064,12 @@
         <v>0.003</v>
       </c>
       <c r="E22" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="B23" s="17">
         <v>4</v>
@@ -11229,12 +11081,12 @@
         <v>0.001</v>
       </c>
       <c r="E23" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -11245,7 +11097,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>18</v>
@@ -11265,7 +11117,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B28" s="29">
         <v>17418.4</v>
@@ -11365,7 +11217,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="B33" s="29">
         <v>33069</v>
@@ -11385,7 +11237,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
